--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115112824</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,332 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122700413</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90857</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>562550</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6464935</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122700415</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79278</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>562546</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6464954</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122700414</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90857</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562546</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6464954</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700413</v>
+        <v>122700415</v>
       </c>
       <c r="B3" t="n">
-        <v>90857</v>
+        <v>79278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,28 +810,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562550</v>
+        <v>562546</v>
       </c>
       <c r="R3" t="n">
-        <v>6464935</v>
+        <v>6464954</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -904,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700415</v>
+        <v>122700413</v>
       </c>
       <c r="B4" t="n">
-        <v>79278</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,24 +916,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562546</v>
+        <v>562550</v>
       </c>
       <c r="R4" t="n">
-        <v>6464954</v>
+        <v>6464935</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>122700414</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>122700415</v>
       </c>
       <c r="B4" t="n">
-        <v>79380</v>
+        <v>79384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>122700413</v>
       </c>
       <c r="B5" t="n">
-        <v>90960</v>
+        <v>90964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700414</v>
+        <v>122700413</v>
       </c>
       <c r="B3" t="n">
         <v>90964</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562546</v>
+        <v>562550</v>
       </c>
       <c r="R3" t="n">
-        <v>6464954</v>
+        <v>6464935</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700413</v>
+        <v>122700414</v>
       </c>
       <c r="B5" t="n">
         <v>90964</v>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562550</v>
+        <v>562546</v>
       </c>
       <c r="R5" t="n">
-        <v>6464935</v>
+        <v>6464954</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700413</v>
+        <v>122700415</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>79384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,28 +810,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562550</v>
+        <v>562546</v>
       </c>
       <c r="R3" t="n">
-        <v>6464935</v>
+        <v>6464954</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -904,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700415</v>
+        <v>122700413</v>
       </c>
       <c r="B4" t="n">
-        <v>79384</v>
+        <v>90964</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,24 +916,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562546</v>
+        <v>562550</v>
       </c>
       <c r="R4" t="n">
-        <v>6464954</v>
+        <v>6464935</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700415</v>
+        <v>122700413</v>
       </c>
       <c r="B3" t="n">
-        <v>79384</v>
+        <v>90964</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,24 +810,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562546</v>
+        <v>562550</v>
       </c>
       <c r="R3" t="n">
-        <v>6464954</v>
+        <v>6464935</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -900,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700413</v>
+        <v>122700415</v>
       </c>
       <c r="B4" t="n">
-        <v>90964</v>
+        <v>79384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,28 +920,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562550</v>
+        <v>562546</v>
       </c>
       <c r="R4" t="n">
-        <v>6464935</v>
+        <v>6464954</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700413</v>
+        <v>122700414</v>
       </c>
       <c r="B3" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562550</v>
+        <v>562546</v>
       </c>
       <c r="R3" t="n">
-        <v>6464935</v>
+        <v>6464954</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700414</v>
+        <v>122700413</v>
       </c>
       <c r="B5" t="n">
-        <v>90964</v>
+        <v>90972</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562546</v>
+        <v>562550</v>
       </c>
       <c r="R5" t="n">
-        <v>6464954</v>
+        <v>6464935</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700414</v>
+        <v>122700413</v>
       </c>
       <c r="B3" t="n">
         <v>90972</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562546</v>
+        <v>562550</v>
       </c>
       <c r="R3" t="n">
-        <v>6464954</v>
+        <v>6464935</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700413</v>
+        <v>122700414</v>
       </c>
       <c r="B5" t="n">
         <v>90972</v>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562550</v>
+        <v>562546</v>
       </c>
       <c r="R5" t="n">
-        <v>6464935</v>
+        <v>6464954</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122700413</v>
+        <v>122700414</v>
       </c>
       <c r="B3" t="n">
         <v>90972</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562550</v>
+        <v>562546</v>
       </c>
       <c r="R3" t="n">
-        <v>6464935</v>
+        <v>6464954</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700414</v>
+        <v>122700413</v>
       </c>
       <c r="B5" t="n">
         <v>90972</v>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562546</v>
+        <v>562550</v>
       </c>
       <c r="R5" t="n">
-        <v>6464954</v>
+        <v>6464935</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115112824</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115112824</v>
+        <v>122700413</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +708,19 @@
           <t>3</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Risten, Ög</t>
+          <t>Risten , Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562558</v>
+        <v>562550</v>
       </c>
       <c r="R2" t="n">
-        <v>6464923</v>
+        <v>6464935</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,17 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 hanar och en hona som gjorde spelflyggningar under mycket ropande och tjadrande samt viss trummning</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +761,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,12 +783,7 @@
         <v>122700414</v>
       </c>
       <c r="B3" t="n">
-        <v>90972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122700415</v>
+        <v>122700417</v>
       </c>
       <c r="B4" t="n">
-        <v>79384</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,24 +896,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562546</v>
+        <v>562523</v>
       </c>
       <c r="R4" t="n">
-        <v>6464954</v>
+        <v>6464999</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1010,42 +990,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122700413</v>
+        <v>82059269</v>
       </c>
       <c r="B5" t="n">
-        <v>90972</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1053,17 +1028,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Risten , Ög</t>
+          <t>Risten, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562550</v>
+        <v>562532</v>
       </c>
       <c r="R5" t="n">
-        <v>6464935</v>
+        <v>6464897</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2018-03-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2018-03-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,6 +1092,1291 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129685021</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björksveden, Björksveden, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562526</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6464898</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122700415</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>562546</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6464954</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113248919</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>562513</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6464940</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En hane i sitt häckningsrevir och födosöksområde</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113398088</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>562525</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6464903</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-11-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Nog samma hane som har revir här och sågs vid flera tillfällen tidigare</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113544064</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>562522</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6464930</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hanen som har revir och födosöksområde i reservatsförslaget. Den brukar ses och höras i området nästan dagligen.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115112824</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>562558</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6464923</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 hanar och en hona som gjorde spelflyggningar under mycket ropande och tjadrande samt viss trummning</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>92456297</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>562523</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6464941</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spår, äldre. Idag liggande träd.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jens Johannesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110908846</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>562511</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6464967</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-07-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113249042</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>562536</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6464923</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde som Södra tänker avverka. Gång på gång har man avverkad I reviret under falska förespeglingar om akuta barkborreangrepp men när man hugger på vintern finns inga  barkborrar längre i träden.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113398077</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>562543</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6464911</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-11-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ett par i sitt häckningsrevir och födosöksområde</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>110631484</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Risten, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562513</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6464945</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113248944</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Risten , Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>562513</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6464940</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Björsäter</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-11-11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Inne i av Södra planerad avverkningsanmälnan A37222-2023. Skoglig värdekärna klassat som V1 av Länsstyrelsen.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 614-2024 artfynd.xlsx
+++ b/artfynd/A 614-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700413</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700414</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700417</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82059269</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129685021</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122700415</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113248919</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,6 +1546,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113398088</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1628,6 +1673,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113544064</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115112824</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1847,6 +1902,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92456297</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110908846</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2054,6 +2119,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113249042</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,6 +2234,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113398077</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2270,6 +2345,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110631484</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2377,8 +2457,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113248944</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>